--- a/Encuesta_Calidad.xlsx
+++ b/Encuesta_Calidad.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maore\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Encuesta_Calidad_EPBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2437E92-098F-4F8B-BE6D-B39397FD13D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5A0A17-607E-4C1C-A115-26CFC570F074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Identificación" sheetId="1" r:id="rId1"/>
     <sheet name="Infraestructura" sheetId="3" r:id="rId2"/>
     <sheet name="Computadores" sheetId="2" r:id="rId3"/>
-    <sheet name=" Recursos Pedagógicos" sheetId="4" r:id="rId4"/>
+    <sheet name="Recursos Pedagógicos" sheetId="4" r:id="rId4"/>
     <sheet name="Programas" sheetId="5" r:id="rId5"/>
     <sheet name="Docentes" sheetId="6" r:id="rId6"/>
   </sheets>

--- a/Encuesta_Calidad.xlsx
+++ b/Encuesta_Calidad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Encuesta_Calidad_EPBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5A0A17-607E-4C1C-A115-26CFC570F074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97968F8B-47B3-42DB-ABE1-77D8888CE329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Identificación" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="144">
   <si>
     <t>Variable</t>
   </si>
@@ -480,9 +480,6 @@
   </si>
   <si>
     <t>¿Los docentes utilizan recursos didactivcos en sus clases?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los docentes diseñan guias propias para sus estudiantes </t>
   </si>
   <si>
     <t xml:space="preserve">Estrategias para enseñar a estudiantes con discapacidad  en sus ritmos de aprendizaje;
@@ -711,8 +708,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabla_Materiales" displayName="Tabla_Materiales" ref="A3:G11">
-  <autoFilter ref="A3:G11" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabla_Materiales" displayName="Tabla_Materiales" ref="A3:G10">
+  <autoFilter ref="A3:G10" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Variable"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Pregunta / campo"/>
@@ -1716,7 +1713,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1732,7 +1729,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1795,7 +1792,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -1804,7 +1801,7 @@
         <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
@@ -1816,7 +1813,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -1837,7 +1834,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G6" s="2"/>
     </row>
@@ -1858,7 +1855,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G7" s="2"/>
     </row>
@@ -1879,7 +1876,7 @@
         <v>8</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -1900,7 +1897,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G9" s="2"/>
     </row>
@@ -1921,14 +1918,9 @@
         <v>8</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>136</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2094,10 +2086,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -2114,10 +2106,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -2264,7 +2256,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>8</v>

--- a/Encuesta_Calidad.xlsx
+++ b/Encuesta_Calidad.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30113"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Encuesta_Calidad_EPBM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yulic\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97968F8B-47B3-42DB-ABE1-77D8888CE329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{58C4A8CE-189E-4805-A4B2-D2D1E0915E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Identificación" sheetId="1" r:id="rId1"/>
     <sheet name="Infraestructura" sheetId="3" r:id="rId2"/>
     <sheet name="Computadores" sheetId="2" r:id="rId3"/>
-    <sheet name="Recursos Pedagógicos" sheetId="4" r:id="rId4"/>
+    <sheet name=" Recursos Pedagógicos" sheetId="4" r:id="rId4"/>
     <sheet name="Programas" sheetId="5" r:id="rId5"/>
     <sheet name="Docentes" sheetId="6" r:id="rId6"/>
   </sheets>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="171">
   <si>
     <t>Variable</t>
   </si>
@@ -133,9 +133,6 @@
     <t>comp_disp</t>
   </si>
   <si>
-    <t>¿La institución cuenta con computadores para uso de estudiantes?</t>
-  </si>
-  <si>
     <t>Sí; No</t>
   </si>
   <si>
@@ -145,9 +142,6 @@
     <t>comp_cantidad</t>
   </si>
   <si>
-    <t>Número actual de computadores, portátiles o tabletas para uso estudiantil</t>
-  </si>
-  <si>
     <t>comp_suficiencia</t>
   </si>
   <si>
@@ -157,9 +151,6 @@
     <t>Sí; Parcialmente; No</t>
   </si>
   <si>
-    <t>Sí; No; Intermitente</t>
-  </si>
-  <si>
     <t>comp_func</t>
   </si>
   <si>
@@ -178,9 +169,6 @@
     <t>¿Los docentes usan computadores o TIC en sus clases?</t>
   </si>
   <si>
-    <t>¿La institución cuenta con servicio de agua?</t>
-  </si>
-  <si>
     <t>Infraestructura</t>
   </si>
   <si>
@@ -238,45 +226,12 @@
     <t>infra_energia</t>
   </si>
   <si>
-    <t>¿La institución cuenta con energía eléctrica?</t>
-  </si>
-  <si>
-    <t>infra_banos</t>
-  </si>
-  <si>
-    <t>¿Los baños están en funcionamiento?</t>
-  </si>
-  <si>
-    <t>infra_aulas_suf</t>
-  </si>
-  <si>
-    <t>¿El número de aulas es suficiente para la cantidad de estudiantes?</t>
-  </si>
-  <si>
-    <t>infra_estado</t>
-  </si>
-  <si>
-    <t>¿Las aulas están en buen estado (paredes, techo, piso)?</t>
-  </si>
-  <si>
     <t>infra_mobiliario</t>
   </si>
   <si>
     <t>¿Los estudiantes cuentan con pupitres o mesas en buen estado?</t>
   </si>
   <si>
-    <t>infra_admin</t>
-  </si>
-  <si>
-    <t>¿La institución cuenta con espacios administrativos (oficina, rectoría o secretaría)?</t>
-  </si>
-  <si>
-    <t>infra_docentes</t>
-  </si>
-  <si>
-    <t>¿La institución cuenta con un espacio para docentes (sala o área de reuniones)?</t>
-  </si>
-  <si>
     <t>infra_biblioteca</t>
   </si>
   <si>
@@ -301,15 +256,6 @@
     <t>infra_recreacion</t>
   </si>
   <si>
-    <t>¿Cuenta con espacios recreativos o deportivos?</t>
-  </si>
-  <si>
-    <t>infra_recreacion_suf</t>
-  </si>
-  <si>
-    <t>¿Estos espacios son suficientes para los estudiantes?</t>
-  </si>
-  <si>
     <t>Preguntas por eje - Infraestructura suficiente</t>
   </si>
   <si>
@@ -319,9 +265,6 @@
     <t>doc_experiencia</t>
   </si>
   <si>
-    <t>Experiencia promedio del cuerpo docente</t>
-  </si>
-  <si>
     <t>0–2 años; 3–5 años; 6–10 años; Más de 10 años</t>
   </si>
   <si>
@@ -349,72 +292,24 @@
     <t>Preguntas por eje - Identificación y control</t>
   </si>
   <si>
-    <t>Pensando en los docentes de esta escuela, ¿cuántos de ellos necesitan formación en las
-siguientes áreas?</t>
-  </si>
-  <si>
     <t>doc_areas_capacitaciones</t>
   </si>
   <si>
     <t>infra_tiempo_energia</t>
   </si>
   <si>
-    <t>En promedio ¿cuántas horas al día cuenta con energía eléctrica estable?</t>
-  </si>
-  <si>
     <t>lista</t>
   </si>
   <si>
     <t>0; Entre 1 y 3;Entre 3 y 5;Entre 5 y 8; más de 8  horas</t>
   </si>
   <si>
-    <t>comp_</t>
-  </si>
-  <si>
     <t>rec_básicos</t>
   </si>
   <si>
     <t>¿Cuenta con recursos básicos en el aula (Pizarra, Marcadores, entre otros)?</t>
   </si>
   <si>
-    <t>horas_escuela</t>
-  </si>
-  <si>
-    <t>horas_clase</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">¿Cuántas horas cronológicas (de 60 minutos) pasan diariamente los estudiantes en la escuela? (incluya recreos, meriendas y otras actividades escolares. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>No incluya actividades extracurriculares</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">). </t>
-    </r>
-  </si>
-  <si>
-    <t>4 horas o menos;
-5 horas;
-8 horas o más;
-6 o 7 horas</t>
-  </si>
-  <si>
     <t>Distribución del tiempo</t>
   </si>
   <si>
@@ -422,12 +317,6 @@
   </si>
   <si>
     <t xml:space="preserve">Selección </t>
-  </si>
-  <si>
-    <t>En los últimos 2 años, ¿cuántos docentes han realizado estudios de Formación Continua?</t>
-  </si>
-  <si>
-    <t>¿Qué tipo de Jornadas Escolares Complementarias ofrece la institución?</t>
   </si>
   <si>
     <t>Ninguno funciona;
@@ -436,18 +325,6 @@
 Todos funcionan</t>
   </si>
   <si>
-    <t>Nada suficiente; Poco suficiente; Suficiente; Muy suficiente</t>
-  </si>
-  <si>
-    <t>Ninguno funciona;Algunos funcionan; La mayoría funciona; Todos funcionan</t>
-  </si>
-  <si>
-    <t>Muy mal estado; Mal estado; Buen estado; Muy buen estado</t>
-  </si>
-  <si>
-    <t>Nada adecuada; Poco adecuada; Adecuada; Muy adecuada</t>
-  </si>
-  <si>
     <t>Nada suficientes; Poco suficientes; Suficientes; Muy suficientes</t>
   </si>
   <si>
@@ -455,9 +332,6 @@
   </si>
   <si>
     <t>Nunca; Rara vez; A veces; Frecuentemente</t>
-  </si>
-  <si>
-    <t>Del total de horas cronológicas diarias (de 60 minutos) que los estudiantes permanecen en la institución educativa, ¿cuántas se destinan efectivamente a actividades pedagógicas estructuradas (tiempo de clase)?</t>
   </si>
   <si>
     <t>Académicas; 
@@ -470,9 +344,6 @@
     <t>educacion_tecnica</t>
   </si>
   <si>
-    <t>¿La institución ofrece modalidades de educación técnica que impliquen horas adicionales de formación, más allá de las clases académicas tradicionales?</t>
-  </si>
-  <si>
     <t>¿Cuenta con recursos didácticos en el aula (proyectores, material de laboratorio, artistica, de deportes, de matemáticas u otros)?</t>
   </si>
   <si>
@@ -482,40 +353,238 @@
     <t>¿Los docentes utilizan recursos didactivcos en sus clases?</t>
   </si>
   <si>
-    <t xml:space="preserve">Estrategias para enseñar a estudiantes con discapacidad  en sus ritmos de aprendizaje;
-Elaboración de planificación de clases;
-Evaluación foramtiva para los aprendizajes y retroalimentación a los estudiantes;
-Habilidades de TICcomo herrramienta para sus clases  (tecnologías de la información y comunicación);
-Estrategias para atender a un aula diversa (Estudantes con diacapacidad, estudantes multilinguis, o aulas multigrado, indigenas, afro,  para enseñar a estudiantes diversos socioeconómicamente, multiculturales o multilingües;
+    <t xml:space="preserve">Los docentes diseñan guias propias para sus estudiantes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> recursos pedagógicos</t>
+  </si>
+  <si>
+    <t>Cuenta con libros especializados para los y las docentes</t>
+  </si>
+  <si>
+    <t>dot_mat_5a</t>
+  </si>
+  <si>
+    <t>¿Las condiciones del colegio (espacios, mobiliario, energía) permiten usar adecuadamente los materiales?</t>
+  </si>
+  <si>
+    <t>Nada adecuadas; Poco adecuadas; Adecuadas; Muy adecuadas</t>
+  </si>
+  <si>
+    <t>Materiales</t>
+  </si>
+  <si>
+    <t>mat_actualizados</t>
+  </si>
+  <si>
+    <t>¿Los materiales son pertinentes para las clases?</t>
+  </si>
+  <si>
+    <t>jornada</t>
+  </si>
+  <si>
+    <t>Respecto del funcionamiento del establecimiento educativo, ¿en qué jornada atiende a los y las estudiantes?</t>
+  </si>
+  <si>
+    <t>Jornada mañana;
+Jornada tarde;
+Jornada única;</t>
+  </si>
+  <si>
+    <t>Tiempo escolar_escuela</t>
+  </si>
+  <si>
+    <t>¿Considera que resignificar el tiempo escolar es tener jornada única?</t>
+  </si>
+  <si>
+    <t>Tiempo escolar_clase</t>
+  </si>
+  <si>
+    <t>Resignificar el tiempo escolar es trascender la estructura cronológica y orientar la generación de experiencias formativas vivas, participativas y contextualizadas a través de proyectos que permiten la integración de áreas disciplinares.
+De acuerdo con lo anterior, ¿en su EE han resignificado el tiempo escolar?</t>
+  </si>
+  <si>
+    <t>Tiempo escolar-Formación integral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En el marco de la formación integral, la resignificación del tiempo escolar implica asumir la diversidad como principio organizador, reconociendo que un tiempo uniforme no garantiza aprendizajes equitativos y proponiendo una gestión flexible que respete las singularidades de cada trayectoria educativa, es decir, La resignificación del tiempo escolar se fundamenta en la transformación cualitativa de la jornada educativa, superando la visión tradicional de la permanencia pasiva para transitar hacia un modelo de aprendizaje activo, diverso y protegido.
+Con este marco, en su EE el tiempo escolar para la formación integral se organiza: 
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Su EE trabaja la formación Integral </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Del total de pc cuntos fincionan </t>
-  </si>
-  <si>
-    <t>¿Cuenta con libros de consulta especializados (diferentes a libros de texto) en áreas como pedagogía, ciencias naturales, matemáticas, entre otras?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> recursos pedagógicos</t>
-  </si>
-  <si>
-    <t>Formación Integral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El EE desarrolla estrategias que genera la convivencia y praticas restaurativas </t>
+    <t>acts_extracurriculares</t>
+  </si>
+  <si>
+    <t>¿La institución desarrolla el programa de Jornada Escolar Complementaria?</t>
+  </si>
+  <si>
+    <t>Si la respuesta es sí, pasar a pregunta acts_extracurriculares_tipo</t>
+  </si>
+  <si>
+    <t>¿En su  EE qué tipo de actividades se desarrollan en el programa de Jornada Escolar Complementaria?</t>
+  </si>
+  <si>
+    <t>Si en la anterior la respuesta fue afirmativa</t>
+  </si>
+  <si>
+    <t>¿La institución tiene modalidades de educación técnica que impliquen horas adicionales de formación, más allá de la jornada ecolar de 6 horas?</t>
+  </si>
+  <si>
+    <t>doc_certificados</t>
+  </si>
+  <si>
+    <t>Proporción de docentes con formación adicional certificada (cursos, diplomados, posgrados)</t>
+  </si>
+  <si>
+    <t>Estrategias para enseñar a estudiantes con discapacidad;
+Diseño de microcurrículos;
+Evaluación formativa para los aprendizajes;
+Uso de TIC (tecnologías de la información y comunicación) en la práctica pedagógica;
+Trabajo pedagógico por proyectos, por retos, por problemas
+Normatividad y política pública educativa
+Estrategias didácticas innovadoras
+Educación ambiental
+Diversidad
+Educación para la Ciudadanía
+Educación para la paz
+Currículos pertinentes, flexibles, contextualizados y antirracistas</t>
+  </si>
+  <si>
+    <t>¿Todas las sedes cuentan con servicio de agua?</t>
+  </si>
+  <si>
+    <t>¿Todas las sedes cuentan con energía eléctrica?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sí, permanente / Sí, intermitente / No </t>
+  </si>
+  <si>
+    <t>En promedio ¿cuántas horas al día cuenta con energía eléctrica estable para todas sus sedes?</t>
+  </si>
+  <si>
+    <t>¿En la integralidad de sedes que conforman la institución en que ambientes especializados hay insuficiencia o inexistencia?</t>
+  </si>
+  <si>
+    <t>Casillas de Verificación</t>
+  </si>
+  <si>
+    <t>(1) Laboratorios; (2) Bibliotecas; (3) Talleres; (4) Salas TIM; (5) Espacios deportivos; (6) Comedores escolares; (7) Zonas recreativas</t>
+  </si>
+  <si>
+    <t>infra_Ambientes</t>
+  </si>
+  <si>
+    <t>¿Qué condiciones físicas afectan mas el aprendizaje?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1) Temperatura; (2) Ruido; (3) Iluminación; (4) Ventilación; (5) Hacinamiento; (6) Ninguna </t>
+  </si>
+  <si>
+    <t>¿La infraestructura permite desarrollar adecuadamente el PEI?</t>
+  </si>
+  <si>
+    <t>Opción múltiple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Sí; 2.No; 3. Parcialmente </t>
+  </si>
+  <si>
+    <t>¿Todas las Sedes cuentan con espacios recreativos o deportivos?</t>
+  </si>
+  <si>
+    <t>infra_Suficiencia</t>
+  </si>
+  <si>
+    <t>¿Existen sedes con sobreocupación o hacinamiento de aulas o espacios?</t>
+  </si>
+  <si>
+    <t>¿Las sedes cuentan con computadores para uso de estudiantes?</t>
+  </si>
+  <si>
+    <t>Número actual de computadores, para uso estudiantil en todas sus sedes</t>
+  </si>
+  <si>
+    <t>tic_uso_docentes</t>
+  </si>
+  <si>
+    <t>Frecuencia con la que los docentes integran TIC en sus clases</t>
+  </si>
+  <si>
+    <t>1. Nunca; 2. Esporádicamente; 3. Mensual; 4. Semanal; 5. Diaria</t>
+  </si>
+  <si>
+    <t>tic_software</t>
+  </si>
+  <si>
+    <t>Plataformas o software educativos en uso (marcar todos)</t>
+  </si>
+  <si>
+    <t>Casillas de verificación</t>
+  </si>
+  <si>
+    <t>1. Colombia Aprende; 2. Software educativo licenciado; 3. Contenidos OVA propios; 4. Recursos digitales gratuitos; 5. Plataformas LMS (Moodle, Classroom, etc.); 6. Ninguno</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>1. 1 hora al día para los centros de interés/ proyectos pedagógicos
+2. Después del descanso
+3. Un día a la semana
+4. El horario de clases se organiza por horas y áreas
+5. El horario de clases se organiza de acuerdo con los centros de interés /proyectos pedagógicos</t>
+  </si>
+  <si>
+    <t>Experiencia promedio del cuerpo docente en todas sus sedes</t>
+  </si>
+  <si>
+    <t>En los últimos 2 años, ¿cuántos docentes han realizado estudios de Formación Continua en todas sus sedes?</t>
+  </si>
+  <si>
+    <t>Pensando en los docentes de todas las sedes del Establecimiento Educativo, ¿en qué ejes considera que necesitan formación?</t>
+  </si>
+  <si>
+    <t>Clima_esc</t>
+  </si>
+  <si>
+    <t>¿Los estudiantes se sienten seguros dentro de la institución educativa?</t>
+  </si>
+  <si>
+    <t>Nunca / Rara vez / A veces / Frecuentemente / Siempre</t>
+  </si>
+  <si>
+    <t>clima escolar</t>
+  </si>
+  <si>
+    <t>¿Se presentan situaciones recurrentes de conflicto, acoso o discriminación?</t>
   </si>
   <si>
     <t>Convivencia</t>
+  </si>
+  <si>
+    <t>convivencia</t>
+  </si>
+  <si>
+    <t>¿La institución cuenta con estrategias para atender estudiantes con discapacidad, talentos excepcionales, rezago o barreras de aprendizaje?</t>
+  </si>
+  <si>
+    <t>Inclusión</t>
+  </si>
+  <si>
+    <t>inclusion</t>
+  </si>
+  <si>
+    <t>Ninguna sede / Menos del 50% / Entre 50% y 79% / 80% o más / Todas las sedes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -552,15 +621,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -572,8 +644,32 @@
         <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -590,11 +686,87 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -623,28 +795,190 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="12">
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -663,7 +997,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla_Identificación" displayName="Tabla_Identificación" ref="A3:G7">
   <autoFilter ref="A3:G7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Variable"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Variable" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Pregunta / campo"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tipo de respuesta"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Opciones o criterio"/>
@@ -676,10 +1010,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla_Infraestructura" displayName="Tabla_Infraestructura" ref="A3:G17">
-  <autoFilter ref="A3:G17" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla_Infraestructura" displayName="Tabla_Infraestructura" ref="A3:G15">
+  <autoFilter ref="A3:G15" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Variable" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Variable" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Pregunta"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Tipo"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Opciones"/>
@@ -695,7 +1029,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_Computadores" displayName="Tabla_Computadores" ref="A3:G11">
   <autoFilter ref="A3:G11" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Variable"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Variable" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Pregunta / campo"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tipo de respuesta"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Opciones o criterio"/>
@@ -708,11 +1042,11 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabla_Materiales" displayName="Tabla_Materiales" ref="A3:G10">
-  <autoFilter ref="A3:G10" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabla_Materiales" displayName="Tabla_Materiales" ref="A3:G13">
+  <autoFilter ref="A3:G13" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Variable"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Pregunta / campo"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Pregunta / campo" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Tipo de respuesta"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Opciones o criterio"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Obligatorio"/>
@@ -724,24 +1058,24 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_Programas" displayName="Tabla_Programas" ref="A3:G10">
-  <autoFilter ref="A3:G10" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_Programas" displayName="Tabla_Programas" ref="A3:G14" dataDxfId="7">
+  <autoFilter ref="A3:G14" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Variable"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Pregunta / campo"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Tipo de respuesta"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Opciones o criterio"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Obligatorio"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Dimensión"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Observaciones"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Variable" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Pregunta / campo" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Tipo de respuesta" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Opciones o criterio" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Obligatorio" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Dimensión" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Observaciones" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabla_Docentes" displayName="Tabla_Docentes" ref="A3:G7">
-  <autoFilter ref="A3:G7" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabla_Docentes" displayName="Tabla_Docentes" ref="A3:G8">
+  <autoFilter ref="A3:G8" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Variable"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Pregunta / campo"/>
@@ -1040,6 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1053,15 +1388,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="A1" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1087,7 +1422,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1110,7 +1445,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1133,7 +1468,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1156,7 +1491,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1189,7 +1524,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G17"/>
+  <sheetPr codeName="Hoja2"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1202,27 +1538,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="A1" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>4</v>
@@ -1236,283 +1572,243 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>123</v>
+      <c r="D5" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="G5" s="8"/>
+    </row>
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>86</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="8"/>
+        <v>43</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>108</v>
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>73</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>122</v>
+        <v>31</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>124</v>
+      <c r="D9" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D10" t="s">
-        <v>91</v>
+      <c r="D10" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>125</v>
+      <c r="D11" s="4" t="s">
+        <v>170</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>32</v>
+        <v>134</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>32</v>
+        <v>134</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>32</v>
+        <v>140</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>38</v>
+        <v>140</v>
+      </c>
+      <c r="D15" t="s">
+        <v>170</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1528,11 +1824,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Hoja3"/>
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="2" max="2" width="56.33203125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -1541,15 +1838,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1575,32 +1872,32 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="10" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="B5" s="2" t="s">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>28</v>
@@ -1612,108 +1909,132 @@
         <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>36</v>
+      <c r="A6" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>128</v>
+      <c r="D9" t="s">
+        <v>95</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
-        <v>127</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>138</v>
+    <row r="10" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="E11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1729,7 +2050,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G10"/>
+  <sheetPr codeName="Hoja4"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1742,15 +2064,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1777,150 +2099,209 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>139</v>
+        <v>46</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>104</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>88</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>133</v>
+        <v>49</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>134</v>
+        <v>50</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>135</v>
+        <v>51</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1935,7 +2316,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G10"/>
+  <sheetPr codeName="Hoja5"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1948,15 +2330,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1981,148 +2363,236 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="26"/>
+    </row>
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="B5" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="C5" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="26"/>
+    </row>
+    <row r="6" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>132</v>
+      <c r="B6" s="14" t="s">
+        <v>117</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>57</v>
-      </c>
       <c r="B8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>141</v>
-      </c>
-      <c r="B9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>143</v>
-      </c>
-      <c r="B10" t="s">
-        <v>142</v>
+        <v>53</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
-      </c>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="19"/>
+    </row>
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="G14" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2137,7 +2607,8 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H7"/>
+  <sheetPr codeName="Hoja6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -2150,15 +2621,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -2183,89 +2654,110 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G5" s="4"/>
+      <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="216" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="E7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Encuesta_Calidad.xlsx
+++ b/Encuesta_Calidad.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yulic\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Encuesta_Calidad_EPBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58C4A8CE-189E-4805-A4B2-D2D1E0915E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7DA947-03F4-4362-A648-8FED334BAD12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Identificación" sheetId="1" r:id="rId1"/>
@@ -456,9 +456,6 @@
     <t>¿Todas las sedes cuentan con energía eléctrica?</t>
   </si>
   <si>
-    <t xml:space="preserve">Sí, permanente / Sí, intermitente / No </t>
-  </si>
-  <si>
     <t>En promedio ¿cuántas horas al día cuenta con energía eléctrica estable para todas sus sedes?</t>
   </si>
   <si>
@@ -531,53 +528,56 @@
     <t>SI</t>
   </si>
   <si>
-    <t>1. 1 hora al día para los centros de interés/ proyectos pedagógicos
+    <t>Experiencia promedio del cuerpo docente en todas sus sedes</t>
+  </si>
+  <si>
+    <t>En los últimos 2 años, ¿cuántos docentes han realizado estudios de Formación Continua en todas sus sedes?</t>
+  </si>
+  <si>
+    <t>Pensando en los docentes de todas las sedes del Establecimiento Educativo, ¿en qué ejes considera que necesitan formación?</t>
+  </si>
+  <si>
+    <t>Clima_esc</t>
+  </si>
+  <si>
+    <t>¿Los estudiantes se sienten seguros dentro de la institución educativa?</t>
+  </si>
+  <si>
+    <t>clima escolar</t>
+  </si>
+  <si>
+    <t>¿Se presentan situaciones recurrentes de conflicto, acoso o discriminación?</t>
+  </si>
+  <si>
+    <t>Convivencia</t>
+  </si>
+  <si>
+    <t>convivencia</t>
+  </si>
+  <si>
+    <t>¿La institución cuenta con estrategias para atender estudiantes con discapacidad, talentos excepcionales, rezago o barreras de aprendizaje?</t>
+  </si>
+  <si>
+    <t>Inclusión</t>
+  </si>
+  <si>
+    <t>inclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sí, permanente ; Sí, intermitente ; No </t>
+  </si>
+  <si>
+    <t>Ninguna sede ; Menos del 50% ; Entre 50% y 79% ; 80% o más ; Todas las sedes</t>
+  </si>
+  <si>
+    <t>1. 1 hora al día para los centros de interés; proyectos pedagógicos
 2. Después del descanso
 3. Un día a la semana
 4. El horario de clases se organiza por horas y áreas
-5. El horario de clases se organiza de acuerdo con los centros de interés /proyectos pedagógicos</t>
-  </si>
-  <si>
-    <t>Experiencia promedio del cuerpo docente en todas sus sedes</t>
-  </si>
-  <si>
-    <t>En los últimos 2 años, ¿cuántos docentes han realizado estudios de Formación Continua en todas sus sedes?</t>
-  </si>
-  <si>
-    <t>Pensando en los docentes de todas las sedes del Establecimiento Educativo, ¿en qué ejes considera que necesitan formación?</t>
-  </si>
-  <si>
-    <t>Clima_esc</t>
-  </si>
-  <si>
-    <t>¿Los estudiantes se sienten seguros dentro de la institución educativa?</t>
-  </si>
-  <si>
-    <t>Nunca / Rara vez / A veces / Frecuentemente / Siempre</t>
-  </si>
-  <si>
-    <t>clima escolar</t>
-  </si>
-  <si>
-    <t>¿Se presentan situaciones recurrentes de conflicto, acoso o discriminación?</t>
-  </si>
-  <si>
-    <t>Convivencia</t>
-  </si>
-  <si>
-    <t>convivencia</t>
-  </si>
-  <si>
-    <t>¿La institución cuenta con estrategias para atender estudiantes con discapacidad, talentos excepcionales, rezago o barreras de aprendizaje?</t>
-  </si>
-  <si>
-    <t>Inclusión</t>
-  </si>
-  <si>
-    <t>inclusion</t>
-  </si>
-  <si>
-    <t>Ninguna sede / Menos del 50% / Entre 50% y 79% / 80% o más / Todas las sedes</t>
+5. El horario de clases se organiza de acuerdo con los centros de interés ;proyectos pedagógicos</t>
+  </si>
+  <si>
+    <t>Nunca ; Rara vez ; A veces ; Frecuentemente ; Siempre</t>
   </si>
 </sst>
 </file>
@@ -843,15 +843,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -960,17 +960,17 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -997,7 +997,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla_Identificación" displayName="Tabla_Identificación" ref="A3:G7">
   <autoFilter ref="A3:G7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Variable" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Variable" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Pregunta / campo"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tipo de respuesta"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Opciones o criterio"/>
@@ -1013,7 +1013,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla_Infraestructura" displayName="Tabla_Infraestructura" ref="A3:G15">
   <autoFilter ref="A3:G15" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Variable" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Variable" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Pregunta"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Tipo"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Opciones"/>
@@ -1029,7 +1029,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_Computadores" displayName="Tabla_Computadores" ref="A3:G11">
   <autoFilter ref="A3:G11" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Variable" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Variable" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Pregunta / campo"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tipo de respuesta"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Opciones o criterio"/>
@@ -1388,15 +1388,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1538,14 +1538,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -1581,7 +1581,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>8</v>
@@ -1601,7 +1601,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>8</v>
@@ -1616,7 +1616,7 @@
         <v>85</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>86</v>
@@ -1716,13 +1716,13 @@
         <v>71</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>8</v>
@@ -1733,16 +1733,16 @@
     </row>
     <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>135</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>8</v>
@@ -1753,16 +1753,16 @@
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>138</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>8</v>
@@ -1773,16 +1773,16 @@
     </row>
     <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>8</v>
@@ -1793,16 +1793,16 @@
     </row>
     <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>144</v>
-      </c>
       <c r="C15" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D15" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>8</v>
@@ -1838,15 +1838,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1876,13 +1876,13 @@
         <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>8</v>
@@ -1897,7 +1897,7 @@
         <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>28</v>
@@ -1999,19 +1999,19 @@
     </row>
     <row r="10" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="C10" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>149</v>
-      </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F10" t="s">
         <v>32</v>
@@ -2019,19 +2019,19 @@
     </row>
     <row r="11" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="C11" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="D11" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="D11" s="24" t="s">
-        <v>153</v>
-      </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F11" t="s">
         <v>32</v>
@@ -2064,15 +2064,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2330,15 +2330,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2437,7 +2437,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>8</v>
@@ -2533,64 +2533,64 @@
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G14" s="6"/>
     </row>
@@ -2621,15 +2621,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -2680,7 +2680,7 @@
         <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>11</v>
@@ -2723,7 +2723,7 @@
         <v>77</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -2743,7 +2743,7 @@
         <v>84</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>11</v>

--- a/Encuesta_Calidad.xlsx
+++ b/Encuesta_Calidad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Encuesta_Calidad_EPBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7DA947-03F4-4362-A648-8FED334BAD12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2368A002-7C99-4C2E-AEFD-66E0E94F9EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Identificación" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="173">
   <si>
     <t>Variable</t>
   </si>
@@ -468,9 +468,6 @@
     <t>(1) Laboratorios; (2) Bibliotecas; (3) Talleres; (4) Salas TIM; (5) Espacios deportivos; (6) Comedores escolares; (7) Zonas recreativas</t>
   </si>
   <si>
-    <t>infra_Ambientes</t>
-  </si>
-  <si>
     <t>¿Qué condiciones físicas afectan mas el aprendizaje?</t>
   </si>
   <si>
@@ -578,6 +575,15 @@
   </si>
   <si>
     <t>Nunca ; Rara vez ; A veces ; Frecuentemente ; Siempre</t>
+  </si>
+  <si>
+    <t>infra_Ambientes1</t>
+  </si>
+  <si>
+    <t>infra_Ambientes2</t>
+  </si>
+  <si>
+    <t>infra_Ambientes3</t>
   </si>
 </sst>
 </file>
@@ -1581,7 +1587,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>8</v>
@@ -1601,7 +1607,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>8</v>
@@ -1716,13 +1722,13 @@
         <v>71</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>8</v>
@@ -1733,7 +1739,7 @@
     </row>
     <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>132</v>
@@ -1753,16 +1759,16 @@
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>136</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>133</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>8</v>
@@ -1773,16 +1779,16 @@
     </row>
     <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>8</v>
@@ -1793,16 +1799,16 @@
     </row>
     <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>143</v>
-      </c>
       <c r="C15" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>8</v>
@@ -1876,13 +1882,13 @@
         <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>8</v>
@@ -1897,7 +1903,7 @@
         <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>28</v>
@@ -1999,19 +2005,19 @@
     </row>
     <row r="10" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="C10" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>148</v>
-      </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F10" t="s">
         <v>32</v>
@@ -2019,19 +2025,19 @@
     </row>
     <row r="11" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="C11" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="D11" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="D11" s="24" t="s">
-        <v>152</v>
-      </c>
       <c r="E11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F11" t="s">
         <v>32</v>
@@ -2437,7 +2443,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>8</v>
@@ -2533,64 +2539,64 @@
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G14" s="6"/>
     </row>
@@ -2680,7 +2686,7 @@
         <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>11</v>
@@ -2723,7 +2729,7 @@
         <v>77</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -2743,7 +2749,7 @@
         <v>84</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>11</v>

--- a/Encuesta_Calidad.xlsx
+++ b/Encuesta_Calidad.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Encuesta_Calidad_EPBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2368A002-7C99-4C2E-AEFD-66E0E94F9EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389FFDC2-0277-4C69-8B06-F4A1A232B8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Identificación" sheetId="1" r:id="rId1"/>
     <sheet name="Infraestructura" sheetId="3" r:id="rId2"/>
     <sheet name="Computadores" sheetId="2" r:id="rId3"/>
-    <sheet name=" Recursos Pedagógicos" sheetId="4" r:id="rId4"/>
+    <sheet name="Recursos Pedagógicos" sheetId="4" r:id="rId4"/>
     <sheet name="Programas" sheetId="5" r:id="rId5"/>
     <sheet name="Docentes" sheetId="6" r:id="rId6"/>
   </sheets>

--- a/Encuesta_Calidad.xlsx
+++ b/Encuesta_Calidad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Encuesta_Calidad_EPBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389FFDC2-0277-4C69-8B06-F4A1A232B8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4327D88B-6168-4BCF-9986-AA3D069A7DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="174">
   <si>
     <t>Variable</t>
   </si>
@@ -584,6 +584,9 @@
   </si>
   <si>
     <t>infra_Ambientes3</t>
+  </si>
+  <si>
+    <t>uso_gui_doc</t>
   </si>
 </sst>
 </file>
@@ -2251,6 +2254,9 @@
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>173</v>
+      </c>
       <c r="B11" s="11" t="s">
         <v>102</v>
       </c>

--- a/Encuesta_Calidad.xlsx
+++ b/Encuesta_Calidad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Encuesta_Calidad_EPBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4327D88B-6168-4BCF-9986-AA3D069A7DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B49C83-EDE4-4BBD-AD37-19C8116C8780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Identificación" sheetId="1" r:id="rId1"/>
@@ -567,26 +567,26 @@
     <t>Ninguna sede ; Menos del 50% ; Entre 50% y 79% ; 80% o más ; Todas las sedes</t>
   </si>
   <si>
-    <t>1. 1 hora al día para los centros de interés; proyectos pedagógicos
-2. Después del descanso
-3. Un día a la semana
-4. El horario de clases se organiza por horas y áreas
+    <t>Nunca ; Rara vez ; A veces ; Frecuentemente ; Siempre</t>
+  </si>
+  <si>
+    <t>infra_Ambientes1</t>
+  </si>
+  <si>
+    <t>infra_Ambientes2</t>
+  </si>
+  <si>
+    <t>infra_Ambientes3</t>
+  </si>
+  <si>
+    <t>uso_gui_doc</t>
+  </si>
+  <si>
+    <t>1. 1 hora al día para los centros de interés proyectos pedagógicos;
+2. Después del descanso;
+3. Un día a la semana;
+4. El horario de clases se organiza por horas y áreas;
 5. El horario de clases se organiza de acuerdo con los centros de interés ;proyectos pedagógicos</t>
-  </si>
-  <si>
-    <t>Nunca ; Rara vez ; A veces ; Frecuentemente ; Siempre</t>
-  </si>
-  <si>
-    <t>infra_Ambientes1</t>
-  </si>
-  <si>
-    <t>infra_Ambientes2</t>
-  </si>
-  <si>
-    <t>infra_Ambientes3</t>
-  </si>
-  <si>
-    <t>uso_gui_doc</t>
   </si>
 </sst>
 </file>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>132</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>135</v>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>137</v>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>102</v>
@@ -2449,7 +2449,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>8</v>
@@ -2554,7 +2554,7 @@
         <v>92</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>153</v>
@@ -2575,7 +2575,7 @@
         <v>92</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>153</v>
@@ -2596,7 +2596,7 @@
         <v>92</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>152</v>

--- a/Encuesta_Calidad.xlsx
+++ b/Encuesta_Calidad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Encuesta_Calidad_EPBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B49C83-EDE4-4BBD-AD37-19C8116C8780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B340C42B-3414-4CFB-973D-9E69C4DD195C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Identificación" sheetId="1" r:id="rId1"/>
@@ -436,157 +436,157 @@
     <t>Proporción de docentes con formación adicional certificada (cursos, diplomados, posgrados)</t>
   </si>
   <si>
+    <t>¿Todas las sedes cuentan con servicio de agua?</t>
+  </si>
+  <si>
+    <t>¿Todas las sedes cuentan con energía eléctrica?</t>
+  </si>
+  <si>
+    <t>En promedio ¿cuántas horas al día cuenta con energía eléctrica estable para todas sus sedes?</t>
+  </si>
+  <si>
+    <t>¿En la integralidad de sedes que conforman la institución en que ambientes especializados hay insuficiencia o inexistencia?</t>
+  </si>
+  <si>
+    <t>Casillas de Verificación</t>
+  </si>
+  <si>
+    <t>(1) Laboratorios; (2) Bibliotecas; (3) Talleres; (4) Salas TIM; (5) Espacios deportivos; (6) Comedores escolares; (7) Zonas recreativas</t>
+  </si>
+  <si>
+    <t>¿Qué condiciones físicas afectan mas el aprendizaje?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1) Temperatura; (2) Ruido; (3) Iluminación; (4) Ventilación; (5) Hacinamiento; (6) Ninguna </t>
+  </si>
+  <si>
+    <t>¿La infraestructura permite desarrollar adecuadamente el PEI?</t>
+  </si>
+  <si>
+    <t>Opción múltiple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Sí; 2.No; 3. Parcialmente </t>
+  </si>
+  <si>
+    <t>¿Todas las Sedes cuentan con espacios recreativos o deportivos?</t>
+  </si>
+  <si>
+    <t>infra_Suficiencia</t>
+  </si>
+  <si>
+    <t>¿Existen sedes con sobreocupación o hacinamiento de aulas o espacios?</t>
+  </si>
+  <si>
+    <t>¿Las sedes cuentan con computadores para uso de estudiantes?</t>
+  </si>
+  <si>
+    <t>Número actual de computadores, para uso estudiantil en todas sus sedes</t>
+  </si>
+  <si>
+    <t>tic_uso_docentes</t>
+  </si>
+  <si>
+    <t>Frecuencia con la que los docentes integran TIC en sus clases</t>
+  </si>
+  <si>
+    <t>1. Nunca; 2. Esporádicamente; 3. Mensual; 4. Semanal; 5. Diaria</t>
+  </si>
+  <si>
+    <t>tic_software</t>
+  </si>
+  <si>
+    <t>Plataformas o software educativos en uso (marcar todos)</t>
+  </si>
+  <si>
+    <t>Casillas de verificación</t>
+  </si>
+  <si>
+    <t>1. Colombia Aprende; 2. Software educativo licenciado; 3. Contenidos OVA propios; 4. Recursos digitales gratuitos; 5. Plataformas LMS (Moodle, Classroom, etc.); 6. Ninguno</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>Experiencia promedio del cuerpo docente en todas sus sedes</t>
+  </si>
+  <si>
+    <t>En los últimos 2 años, ¿cuántos docentes han realizado estudios de Formación Continua en todas sus sedes?</t>
+  </si>
+  <si>
+    <t>Pensando en los docentes de todas las sedes del Establecimiento Educativo, ¿en qué ejes considera que necesitan formación?</t>
+  </si>
+  <si>
+    <t>Clima_esc</t>
+  </si>
+  <si>
+    <t>¿Los estudiantes se sienten seguros dentro de la institución educativa?</t>
+  </si>
+  <si>
+    <t>clima escolar</t>
+  </si>
+  <si>
+    <t>¿Se presentan situaciones recurrentes de conflicto, acoso o discriminación?</t>
+  </si>
+  <si>
+    <t>Convivencia</t>
+  </si>
+  <si>
+    <t>convivencia</t>
+  </si>
+  <si>
+    <t>¿La institución cuenta con estrategias para atender estudiantes con discapacidad, talentos excepcionales, rezago o barreras de aprendizaje?</t>
+  </si>
+  <si>
+    <t>Inclusión</t>
+  </si>
+  <si>
+    <t>inclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sí, permanente ; Sí, intermitente ; No </t>
+  </si>
+  <si>
+    <t>Ninguna sede ; Menos del 50% ; Entre 50% y 79% ; 80% o más ; Todas las sedes</t>
+  </si>
+  <si>
+    <t>Nunca ; Rara vez ; A veces ; Frecuentemente ; Siempre</t>
+  </si>
+  <si>
+    <t>infra_Ambientes1</t>
+  </si>
+  <si>
+    <t>infra_Ambientes2</t>
+  </si>
+  <si>
+    <t>infra_Ambientes3</t>
+  </si>
+  <si>
+    <t>uso_gui_doc</t>
+  </si>
+  <si>
+    <t>1. 1 hora al día para los centros de interés proyectos pedagógicos;
+2. Después del descanso;
+3. Un día a la semana;
+4. El horario de clases se organiza por horas y áreas;
+5. El horario de clases se organiza de acuerdo con los centros de interés ;proyectos pedagógicos</t>
+  </si>
+  <si>
     <t>Estrategias para enseñar a estudiantes con discapacidad;
 Diseño de microcurrículos;
 Evaluación formativa para los aprendizajes;
 Uso de TIC (tecnologías de la información y comunicación) en la práctica pedagógica;
 Trabajo pedagógico por proyectos, por retos, por problemas
-Normatividad y política pública educativa
-Estrategias didácticas innovadoras
-Educación ambiental
-Diversidad
-Educación para la Ciudadanía
-Educación para la paz
+Normatividad y política pública educativa;
+Estrategias didácticas innovadoras;
+Educación ambiental;
+Diversidad;
+Educación para la Ciudadanía;
+Educación para la paz;
 Currículos pertinentes, flexibles, contextualizados y antirracistas</t>
-  </si>
-  <si>
-    <t>¿Todas las sedes cuentan con servicio de agua?</t>
-  </si>
-  <si>
-    <t>¿Todas las sedes cuentan con energía eléctrica?</t>
-  </si>
-  <si>
-    <t>En promedio ¿cuántas horas al día cuenta con energía eléctrica estable para todas sus sedes?</t>
-  </si>
-  <si>
-    <t>¿En la integralidad de sedes que conforman la institución en que ambientes especializados hay insuficiencia o inexistencia?</t>
-  </si>
-  <si>
-    <t>Casillas de Verificación</t>
-  </si>
-  <si>
-    <t>(1) Laboratorios; (2) Bibliotecas; (3) Talleres; (4) Salas TIM; (5) Espacios deportivos; (6) Comedores escolares; (7) Zonas recreativas</t>
-  </si>
-  <si>
-    <t>¿Qué condiciones físicas afectan mas el aprendizaje?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1) Temperatura; (2) Ruido; (3) Iluminación; (4) Ventilación; (5) Hacinamiento; (6) Ninguna </t>
-  </si>
-  <si>
-    <t>¿La infraestructura permite desarrollar adecuadamente el PEI?</t>
-  </si>
-  <si>
-    <t>Opción múltiple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Sí; 2.No; 3. Parcialmente </t>
-  </si>
-  <si>
-    <t>¿Todas las Sedes cuentan con espacios recreativos o deportivos?</t>
-  </si>
-  <si>
-    <t>infra_Suficiencia</t>
-  </si>
-  <si>
-    <t>¿Existen sedes con sobreocupación o hacinamiento de aulas o espacios?</t>
-  </si>
-  <si>
-    <t>¿Las sedes cuentan con computadores para uso de estudiantes?</t>
-  </si>
-  <si>
-    <t>Número actual de computadores, para uso estudiantil en todas sus sedes</t>
-  </si>
-  <si>
-    <t>tic_uso_docentes</t>
-  </si>
-  <si>
-    <t>Frecuencia con la que los docentes integran TIC en sus clases</t>
-  </si>
-  <si>
-    <t>1. Nunca; 2. Esporádicamente; 3. Mensual; 4. Semanal; 5. Diaria</t>
-  </si>
-  <si>
-    <t>tic_software</t>
-  </si>
-  <si>
-    <t>Plataformas o software educativos en uso (marcar todos)</t>
-  </si>
-  <si>
-    <t>Casillas de verificación</t>
-  </si>
-  <si>
-    <t>1. Colombia Aprende; 2. Software educativo licenciado; 3. Contenidos OVA propios; 4. Recursos digitales gratuitos; 5. Plataformas LMS (Moodle, Classroom, etc.); 6. Ninguno</t>
-  </si>
-  <si>
-    <t>si</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>Experiencia promedio del cuerpo docente en todas sus sedes</t>
-  </si>
-  <si>
-    <t>En los últimos 2 años, ¿cuántos docentes han realizado estudios de Formación Continua en todas sus sedes?</t>
-  </si>
-  <si>
-    <t>Pensando en los docentes de todas las sedes del Establecimiento Educativo, ¿en qué ejes considera que necesitan formación?</t>
-  </si>
-  <si>
-    <t>Clima_esc</t>
-  </si>
-  <si>
-    <t>¿Los estudiantes se sienten seguros dentro de la institución educativa?</t>
-  </si>
-  <si>
-    <t>clima escolar</t>
-  </si>
-  <si>
-    <t>¿Se presentan situaciones recurrentes de conflicto, acoso o discriminación?</t>
-  </si>
-  <si>
-    <t>Convivencia</t>
-  </si>
-  <si>
-    <t>convivencia</t>
-  </si>
-  <si>
-    <t>¿La institución cuenta con estrategias para atender estudiantes con discapacidad, talentos excepcionales, rezago o barreras de aprendizaje?</t>
-  </si>
-  <si>
-    <t>Inclusión</t>
-  </si>
-  <si>
-    <t>inclusion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sí, permanente ; Sí, intermitente ; No </t>
-  </si>
-  <si>
-    <t>Ninguna sede ; Menos del 50% ; Entre 50% y 79% ; 80% o más ; Todas las sedes</t>
-  </si>
-  <si>
-    <t>Nunca ; Rara vez ; A veces ; Frecuentemente ; Siempre</t>
-  </si>
-  <si>
-    <t>infra_Ambientes1</t>
-  </si>
-  <si>
-    <t>infra_Ambientes2</t>
-  </si>
-  <si>
-    <t>infra_Ambientes3</t>
-  </si>
-  <si>
-    <t>uso_gui_doc</t>
-  </si>
-  <si>
-    <t>1. 1 hora al día para los centros de interés proyectos pedagógicos;
-2. Después del descanso;
-3. Un día a la semana;
-4. El horario de clases se organiza por horas y áreas;
-5. El horario de clases se organiza de acuerdo con los centros de interés ;proyectos pedagógicos</t>
   </si>
 </sst>
 </file>
@@ -1584,13 +1584,13 @@
         <v>60</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>8</v>
@@ -1604,13 +1604,13 @@
         <v>61</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>8</v>
@@ -1625,7 +1625,7 @@
         <v>85</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>86</v>
@@ -1725,13 +1725,13 @@
         <v>71</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>8</v>
@@ -1742,16 +1742,16 @@
     </row>
     <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>134</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>8</v>
@@ -1762,16 +1762,16 @@
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>8</v>
@@ -1782,16 +1782,16 @@
     </row>
     <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>8</v>
@@ -1802,16 +1802,16 @@
     </row>
     <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>142</v>
-      </c>
       <c r="C15" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>8</v>
@@ -1885,13 +1885,13 @@
         <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>8</v>
@@ -1906,7 +1906,7 @@
         <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>28</v>
@@ -2008,19 +2008,19 @@
     </row>
     <row r="10" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="C10" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>147</v>
-      </c>
       <c r="E10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F10" t="s">
         <v>32</v>
@@ -2028,19 +2028,19 @@
     </row>
     <row r="11" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="C11" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="D11" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="D11" s="24" t="s">
-        <v>151</v>
-      </c>
       <c r="E11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F11" t="s">
         <v>32</v>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>102</v>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>118</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>8</v>
@@ -2545,64 +2545,64 @@
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G14" s="6"/>
     </row>
@@ -2692,7 +2692,7 @@
         <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>11</v>
@@ -2735,12 +2735,12 @@
         <v>77</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -2755,13 +2755,13 @@
         <v>84</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>8</v>

--- a/Encuesta_Calidad.xlsx
+++ b/Encuesta_Calidad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Encuesta_Calidad_EPBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B340C42B-3414-4CFB-973D-9E69C4DD195C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80A1611-B7EB-43CA-BC12-6B167FF59FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Identificación" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="171">
   <si>
     <t>Variable</t>
   </si>
@@ -448,24 +448,12 @@
     <t>¿En la integralidad de sedes que conforman la institución en que ambientes especializados hay insuficiencia o inexistencia?</t>
   </si>
   <si>
-    <t>Casillas de Verificación</t>
-  </si>
-  <si>
-    <t>(1) Laboratorios; (2) Bibliotecas; (3) Talleres; (4) Salas TIM; (5) Espacios deportivos; (6) Comedores escolares; (7) Zonas recreativas</t>
-  </si>
-  <si>
     <t>¿Qué condiciones físicas afectan mas el aprendizaje?</t>
   </si>
   <si>
-    <t xml:space="preserve">(1) Temperatura; (2) Ruido; (3) Iluminación; (4) Ventilación; (5) Hacinamiento; (6) Ninguna </t>
-  </si>
-  <si>
     <t>¿La infraestructura permite desarrollar adecuadamente el PEI?</t>
   </si>
   <si>
-    <t>Opción múltiple</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. Sí; 2.No; 3. Parcialmente </t>
   </si>
   <si>
@@ -497,9 +485,6 @@
   </si>
   <si>
     <t>Plataformas o software educativos en uso (marcar todos)</t>
-  </si>
-  <si>
-    <t>Casillas de verificación</t>
   </si>
   <si>
     <t>1. Colombia Aprende; 2. Software educativo licenciado; 3. Contenidos OVA propios; 4. Recursos digitales gratuitos; 5. Plataformas LMS (Moodle, Classroom, etc.); 6. Ninguno</t>
@@ -587,6 +572,12 @@
 Educación para la Ciudadanía;
 Educación para la paz;
 Currículos pertinentes, flexibles, contextualizados y antirracistas</t>
+  </si>
+  <si>
+    <t>1. Laboratorios; 2. Bibliotecas; 3. Talleres; 4. Salas TIM; 5. Espacios deportivos; 6. Comedores escolares; 7. Zonas recreativas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Temperatura; 2. Ruido; 3. Iluminación; 4. Ventilación; 5. Hacinamiento; 6. Ninguna </t>
   </si>
 </sst>
 </file>
@@ -775,7 +766,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -833,9 +824,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -844,9 +832,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1397,15 +1382,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1547,14 +1532,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -1590,7 +1575,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>8</v>
@@ -1610,7 +1595,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>8</v>
@@ -1725,13 +1710,13 @@
         <v>71</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>8</v>
@@ -1742,16 +1727,16 @@
     </row>
     <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>131</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>132</v>
+        <v>11</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>8</v>
@@ -1762,16 +1747,16 @@
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>132</v>
+        <v>11</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>8</v>
@@ -1782,16 +1767,16 @@
     </row>
     <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>137</v>
+        <v>11</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>8</v>
@@ -1802,16 +1787,16 @@
     </row>
     <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>137</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>8</v>
@@ -1847,15 +1832,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1885,13 +1870,13 @@
         <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>8</v>
@@ -1906,7 +1891,7 @@
         <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>28</v>
@@ -2007,40 +1992,40 @@
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
-        <v>144</v>
+      <c r="A10" s="21" t="s">
+        <v>140</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>137</v>
+        <v>141</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E10" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E11" t="s">
         <v>147</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="E11" t="s">
-        <v>152</v>
       </c>
       <c r="F11" t="s">
         <v>32</v>
@@ -2073,15 +2058,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2255,7 +2240,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>102</v>
@@ -2342,15 +2327,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2376,46 +2361,46 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="C4" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="26" t="s">
+      <c r="C4" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="E4" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="26" t="s">
+      <c r="E4" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="26"/>
+      <c r="G4" s="24"/>
     </row>
     <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="26" t="s">
+      <c r="C5" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="26" t="s">
+      <c r="E5" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="26"/>
+      <c r="G5" s="24"/>
     </row>
     <row r="6" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -2438,7 +2423,7 @@
       </c>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>118</v>
       </c>
@@ -2449,7 +2434,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>8</v>
@@ -2545,64 +2530,64 @@
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G14" s="6"/>
     </row>
@@ -2633,15 +2618,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -2692,7 +2677,7 @@
         <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>11</v>
@@ -2735,7 +2720,7 @@
         <v>77</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>28</v>
@@ -2755,13 +2740,13 @@
         <v>84</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>8</v>

--- a/Encuesta_Calidad.xlsx
+++ b/Encuesta_Calidad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Encuesta_Calidad_EPBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80A1611-B7EB-43CA-BC12-6B167FF59FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B057F89B-2FFE-4EC1-872D-4F4DB3863407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Identificación" sheetId="1" r:id="rId1"/>
@@ -334,13 +334,6 @@
     <t>Nunca; Rara vez; A veces; Frecuentemente</t>
   </si>
   <si>
-    <t>Académicas; 
-Deportivas; 
-Artísticas; 
-Servicio comunitario;                                                Educación  Ténica;
-Otros</t>
-  </si>
-  <si>
     <t>educacion_tecnica</t>
   </si>
   <si>
@@ -578,6 +571,12 @@
   </si>
   <si>
     <t xml:space="preserve">1.Temperatura; 2. Ruido; 3. Iluminación; 4. Ventilación; 5. Hacinamiento; 6. Ninguna </t>
+  </si>
+  <si>
+    <t>Académicas; 
+Deportivas; 
+Artísticas; 
+Servicio comunitario;                                                Educación  Ténica</t>
   </si>
 </sst>
 </file>
@@ -1569,13 +1568,13 @@
         <v>60</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>8</v>
@@ -1589,13 +1588,13 @@
         <v>61</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>8</v>
@@ -1610,7 +1609,7 @@
         <v>85</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>86</v>
@@ -1710,13 +1709,13 @@
         <v>71</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>8</v>
@@ -1727,16 +1726,16 @@
     </row>
     <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>8</v>
@@ -1747,16 +1746,16 @@
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>8</v>
@@ -1767,16 +1766,16 @@
     </row>
     <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>134</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>8</v>
@@ -1787,16 +1786,16 @@
     </row>
     <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="C15" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>8</v>
@@ -1870,13 +1869,13 @@
         <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>8</v>
@@ -1891,7 +1890,7 @@
         <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>28</v>
@@ -1993,19 +1992,19 @@
     </row>
     <row r="10" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="C10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>142</v>
-      </c>
       <c r="E10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F10" t="s">
         <v>32</v>
@@ -2013,19 +2012,19 @@
     </row>
     <row r="11" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>145</v>
-      </c>
       <c r="E11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F11" t="s">
         <v>32</v>
@@ -2108,7 +2107,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -2117,7 +2116,7 @@
         <v>46</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
@@ -2129,7 +2128,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -2150,7 +2149,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G6" s="2"/>
     </row>
@@ -2171,7 +2170,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G7" s="2"/>
     </row>
@@ -2180,7 +2179,7 @@
         <v>49</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>11</v>
@@ -2192,7 +2191,7 @@
         <v>8</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -2201,7 +2200,7 @@
         <v>50</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>11</v>
@@ -2213,7 +2212,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G9" s="2"/>
     </row>
@@ -2222,7 +2221,7 @@
         <v>51</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>11</v>
@@ -2234,16 +2233,16 @@
         <v>8</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>11</v>
@@ -2255,36 +2254,36 @@
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="C12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>110</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>11</v>
@@ -2296,7 +2295,7 @@
         <v>8</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G13" s="6"/>
     </row>
@@ -2362,16 +2361,16 @@
     </row>
     <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="C4" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="24" t="s">
         <v>112</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>113</v>
       </c>
       <c r="E4" s="24" t="s">
         <v>8</v>
@@ -2383,10 +2382,10 @@
     </row>
     <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="24" t="s">
         <v>114</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>115</v>
       </c>
       <c r="C5" s="24" t="s">
         <v>11</v>
@@ -2404,10 +2403,10 @@
     </row>
     <row r="6" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>117</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>11</v>
@@ -2425,16 +2424,16 @@
     </row>
     <row r="7" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>8</v>
@@ -2446,10 +2445,10 @@
     </row>
     <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>11</v>
@@ -2464,24 +2463,24 @@
         <v>52</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>52</v>
@@ -2509,10 +2508,10 @@
     </row>
     <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>11</v>
@@ -2530,64 +2529,64 @@
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G14" s="6"/>
     </row>
@@ -2653,10 +2652,10 @@
     </row>
     <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>11</v>
@@ -2677,7 +2676,7 @@
         <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>11</v>
@@ -2720,7 +2719,7 @@
         <v>77</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>28</v>
@@ -2740,13 +2739,13 @@
         <v>84</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>8</v>
